--- a/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/03_CMP3 - Tedarikçi ve Dış Kaynak Yönetimi/EKG-STN-PLN-04_dis_kaynak_toz_boya_proses_yeterlilik_giris_kontrol_ve.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/03_CMP3 - Tedarikçi ve Dış Kaynak Yönetimi/EKG-STN-PLN-04_dis_kaynak_toz_boya_proses_yeterlilik_giris_kontrol_ve.xlsx
@@ -1183,7 +1183,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-STN-PLN-04&amp;C&amp;"Arial,Regular"&amp;11Dış Kaynak Toz Boya Proses Yeterlilik, Giriş Kontrol ve Yeniden Onay Planı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 02.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1eb1f63593144cb"/>
   <x:tableParts count="1">
@@ -1711,7 +1712,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-STN-PLN-04&amp;C&amp;"Arial,Regular"&amp;11Dış Kaynak Toz Boya Proses Yeterlilik, Giriş Kontrol ve Yeniden Onay Planı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 02.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0d9caeda1614374"/>
   <x:tableParts count="1">
@@ -2139,7 +2141,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-STN-PLN-04&amp;C&amp;"Arial,Regular"&amp;11Dış Kaynak Toz Boya Proses Yeterlilik, Giriş Kontrol ve Yeniden Onay Planı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 02.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbd07a805f3442b7"/>
   <x:tableParts count="1">
